--- a/nba/Modelo_Props_NBA.xlsx
+++ b/nba/Modelo_Props_NBA.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats Jugadores" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats Equipos" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defensa x Posicion" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -177,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -275,9 +276,15 @@
     <xf numFmtId="166" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -388,7 +395,7 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Fuente: basketball-reference.com, NBA 2026-27 Per Game Stats, descargado 23-oct-2026. Jugadores traspasados: solo su equipo actual. Para actualizar, pega la tabla Per Game desde A1.</t>
+        <t>Fuente: basketball-reference.com, NBA 2026-27 Per Game Stats, descargado 24-oct-2026. Jugadores traspasados: solo su equipo actual. Para actualizar, pega la tabla Per Game desde A1.</t>
       </text>
     </comment>
   </commentList>
@@ -884,23 +891,23 @@
         <v/>
       </c>
       <c r="H8" s="19">
-        <f>(INDEX('Stats Equipos'!$F:$F,$P$12)/INDEX('Stats Equipos'!$C:$C,$P$12))/Parametros!$B$20</f>
+        <f>IF(Parametros!$B$15="Sí",IFERROR(INDEX('Defensa x Posicion'!$C:$AF,$P$12,MATCH($P$14&amp;" PTS",'Defensa x Posicion'!$C$1:$AF$1,0)),1),(INDEX('Stats Equipos'!$F:$F,$P$12)/INDEX('Stats Equipos'!$C:$C,$P$12))/Parametros!$B$20)</f>
         <v/>
       </c>
       <c r="I8" s="19">
-        <f>(1-INDEX('Stats Equipos'!$E:$E,$P$12))/(1-Parametros!$B$19)</f>
+        <f>IF(Parametros!$B$15="Sí",IFERROR(INDEX('Defensa x Posicion'!$C:$AF,$P$12,MATCH($P$14&amp;" REB",'Defensa x Posicion'!$C$1:$AF$1,0)),1),(1-INDEX('Stats Equipos'!$E:$E,$P$12))/(1-Parametros!$B$19))</f>
         <v/>
       </c>
       <c r="J8" s="19">
-        <f>(1-INDEX('Stats Equipos'!$D:$D,$P$12))/(1-Parametros!$B$18)</f>
+        <f>IF(Parametros!$B$15="Sí",IFERROR(INDEX('Defensa x Posicion'!$C:$AF,$P$12,MATCH($P$14&amp;" REB",'Defensa x Posicion'!$C$1:$AF$1,0)),1),(1-INDEX('Stats Equipos'!$D:$D,$P$12))/(1-Parametros!$B$18))</f>
         <v/>
       </c>
       <c r="K8" s="19">
-        <f>(INDEX('Stats Equipos'!$G:$G,$P$12)/INDEX('Stats Equipos'!$C:$C,$P$12))/Parametros!$B$21</f>
+        <f>IF(Parametros!$B$15="Sí",IFERROR(INDEX('Defensa x Posicion'!$C:$AF,$P$12,MATCH($P$14&amp;" AST",'Defensa x Posicion'!$C$1:$AF$1,0)),1),(INDEX('Stats Equipos'!$G:$G,$P$12)/INDEX('Stats Equipos'!$C:$C,$P$12))/Parametros!$B$21)</f>
         <v/>
       </c>
       <c r="L8" s="19">
-        <f>(INDEX('Stats Equipos'!$H:$H,$P$12)/INDEX('Stats Equipos'!$C:$C,$P$12))/Parametros!$B$22</f>
+        <f>IF(Parametros!$B$15="Sí",IFERROR(INDEX('Defensa x Posicion'!$C:$AF,$P$12,MATCH($P$14&amp;" 3PM",'Defensa x Posicion'!$C$1:$AF$1,0)),1),(INDEX('Stats Equipos'!$H:$H,$P$12)/INDEX('Stats Equipos'!$C:$C,$P$12))/Parametros!$B$22)</f>
         <v/>
       </c>
       <c r="M8" s="20">
@@ -1048,6 +1055,11 @@
           <t>Props</t>
         </is>
       </c>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="24" t="inlineStr">
@@ -1114,6 +1126,10 @@
         <is>
           <t>Pick</t>
         </is>
+      </c>
+      <c r="P14" s="14">
+        <f>IFERROR(LEFT(INDEX('Stats Jugadores'!$E:$E,$P$8),FIND("-",INDEX('Stats Jugadores'!$E:$E,$P$8))-1),INDEX('Stats Jugadores'!$E:$E,$P$8))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1521,7 +1537,7 @@
         </is>
       </c>
       <c r="C23" s="26">
-        <f>INDEX('Stats Jugadores'!$Z:$Z,$P$8)*$M$8</f>
+        <f>INDEX('Stats Jugadores'!$Z:$Z,$P$8)*$M$8*IF(Parametros!$B$15="Sí",IFERROR(INDEX('Defensa x Posicion'!$C:$AF,$P$12,MATCH($P$14&amp;" STL",'Defensa x Posicion'!$C$1:$AF$1,0)),1),1)</f>
         <v/>
       </c>
       <c r="D23" s="16">
@@ -1567,7 +1583,7 @@
         </is>
       </c>
       <c r="C24" s="26">
-        <f>INDEX('Stats Jugadores'!$AA:$AA,$P$8)*$M$8</f>
+        <f>INDEX('Stats Jugadores'!$AA:$AA,$P$8)*$M$8*IF(Parametros!$B$15="Sí",IFERROR(INDEX('Defensa x Posicion'!$C:$AF,$P$12,MATCH($P$14&amp;" BLK",'Defensa x Posicion'!$C$1:$AF$1,0)),1),1)</f>
         <v/>
       </c>
       <c r="D24" s="16">
@@ -1616,7 +1632,7 @@
     <row r="27">
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>Datos reales 2026-27 (basketball-reference.com y teamrankings.com, 23-oct-2026). Las líneas y cuotas de ejemplo son ficticias: pon las de tu casa de apuestas.</t>
+          <t>Datos reales 2026-27 (basketball-reference.com y teamrankings.com, 24-oct-2026). Las líneas y cuotas de ejemplo son ficticias: pon las de tu casa de apuestas.</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -1773,95 +1789,102 @@
     <row r="5">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>2. Actualiza 'Stats Equipos' con teamrankings.com: Pace = Possessions per Game; ORB% = Offensive Rebounding %; DRB% = Defensive Rebounding %;</t>
+          <t>• Defensa por posición: la hoja 'Defensa x Posicion' se calcula sola con nba/actualizar.py a partir de los box scores. Actívala o apágala en Parametros (Usar ajuste por posición).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Pts/Ast/3PM permitidos = Opponent Points / Opponent Assists / Opponent Three Pointers Made per Game. La columna Abrev debe coincidir con 'Team' de basketball-reference (CHO, PHO, BRK...).</t>
+          <t>2. Actualiza 'Stats Equipos' con teamrankings.com: Pace = Possessions per Game; ORB% = Offensive Rebounding %; DRB% = Defensive Rebounding %;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>3. En 'Resultado' elige jugador y rival (listas desplegables), escribe minutos esperados (xMP) y si juega de local (Sí/No).</t>
+          <t xml:space="preserve">   Pts/Ast/3PM permitidos = Opponent Points / Opponent Assists / Opponent Three Pointers Made per Game. La columna Abrev debe coincidir con 'Team' de basketball-reference (CHO, PHO, BRK...).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
+          <t>3. En 'Resultado' elige jugador y rival (listas desplegables), escribe minutos esperados (xMP) y si juega de local (Sí/No).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
           <t>4. Escribe la línea de la casa de apuestas y las cuotas americanas (ej. -115, +105). El modelo calcula probabilidad, edge y pick (OVER / UNDER / PASS).</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t>CÓMO CALCULA</t>
-        </is>
-      </c>
+      <c r="A10" s="36" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>• Minuto % = xMP / minutos promedio.   • PACE adj. = pace promedio de ambos equipos / pace del equipo del jugador.</t>
+          <t>CÓMO CALCULA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>• Defensa adj. = puntos permitidos por posesión del rival / promedio de liga (igual para asistencias y triples).</t>
+          <t>• Minuto % = xMP / minutos promedio.   • PACE adj. = pace promedio de ambos equipos / pace del equipo del jugador.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>• Off Reb adj. = (1 − DRB% rival) / (1 − DRB% liga).   Def Reb adj. = (1 − ORB% rival) / (1 − ORB% liga).</t>
+          <t>• Defensa adj. = puntos permitidos por posesión del rival / promedio de liga (igual para asistencias y triples).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>• Factor base = Minuto % × PACE adj. × Local adj.  Cada estadística por partido se multiplica por el factor base y su ajuste.</t>
+          <t>• Off Reb adj. = (1 − DRB% rival) / (1 − DRB% liga).   Def Reb adj. = (1 − ORB% rival) / (1 − ORB% liga).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>• Puntos = (2PA×2P%×2 + 3PA×3P%×3 + FTA×FT%) × Defensa adj.</t>
+          <t>• Factor base = Minuto % × PACE adj. × Local adj.  Cada estadística por partido se multiplica por el factor base y su ajuste.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>• Probabilidad Over = 1 − Normal(línea; proyección; proyección×CV). Los CV están en 'Parametros' y son supuestos editables.</t>
+          <t>• Puntos = (2PA×2P%×2 + 3PA×3P%×3 + FTA×FT%) × Defensa adj.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
+          <t>• Probabilidad Over = 1 − Normal(línea; proyección; proyección×CV). Los CV están en 'Parametros' y son supuestos editables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
           <t>• Prob. implícita: cuota negativa → −c/(−c+100); positiva → 100/(c+100). Edge = prob. modelo − prob. implícita.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="35" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>Herramienta educativa: no garantiza resultados. Apuesta con responsabilidad.</t>
         </is>
@@ -35271,25 +35294,25 @@
         </is>
       </c>
       <c r="C2" s="40" t="n">
-        <v>113.8</v>
+        <v>108.7</v>
       </c>
       <c r="D2" s="41" t="n">
-        <v>0.268</v>
+        <v>0.28</v>
       </c>
       <c r="E2" s="41" t="n">
-        <v>0.775</v>
+        <v>0.705</v>
       </c>
       <c r="F2" s="40" t="n">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G2" s="40" t="n">
-        <v>30</v>
+        <v>25.5</v>
       </c>
       <c r="H2" s="40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" s="40" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3">
@@ -35304,25 +35327,25 @@
         </is>
       </c>
       <c r="C3" s="40" t="n">
-        <v>102.1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D3" s="41" t="n">
-        <v>0.255</v>
+        <v>0.247</v>
       </c>
       <c r="E3" s="41" t="n">
-        <v>0.659</v>
+        <v>0.675</v>
       </c>
       <c r="F3" s="40" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G3" s="40" t="n">
         <v>27</v>
       </c>
       <c r="H3" s="40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I3" s="40" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
@@ -35370,25 +35393,25 @@
         </is>
       </c>
       <c r="C5" s="40" t="n">
-        <v>114.1</v>
+        <v>113.4</v>
       </c>
       <c r="D5" s="41" t="n">
-        <v>0.375</v>
+        <v>0.333</v>
       </c>
       <c r="E5" s="41" t="n">
-        <v>0.6920000000000001</v>
+        <v>0.713</v>
       </c>
       <c r="F5" s="40" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G5" s="40" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="40" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="I5" s="40" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -35403,25 +35426,25 @@
         </is>
       </c>
       <c r="C6" s="40" t="n">
-        <v>104.5</v>
+        <v>104</v>
       </c>
       <c r="D6" s="41" t="n">
-        <v>0.357</v>
+        <v>0.351</v>
       </c>
       <c r="E6" s="41" t="n">
-        <v>0.725</v>
+        <v>0.716</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>103</v>
+        <v>115.5</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>22</v>
+        <v>29.5</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>110</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="7">
@@ -35469,25 +35492,25 @@
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>101.6</v>
+        <v>103.9</v>
       </c>
       <c r="D8" s="41" t="n">
-        <v>0.242</v>
+        <v>0.26</v>
       </c>
       <c r="E8" s="41" t="n">
-        <v>0.595</v>
+        <v>0.667</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>128</v>
+        <v>116.5</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>32</v>
+        <v>29.5</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>110</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="9">
@@ -35535,25 +35558,25 @@
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>102.1</v>
+        <v>105</v>
       </c>
       <c r="D10" s="41" t="n">
-        <v>0.341</v>
+        <v>0.31</v>
       </c>
       <c r="E10" s="41" t="n">
-        <v>0.745</v>
+        <v>0.7170000000000001</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>121</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="11">
@@ -35634,25 +35657,25 @@
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>107.7</v>
+        <v>106.9</v>
       </c>
       <c r="D13" s="41" t="n">
-        <v>0.205</v>
+        <v>0.239</v>
       </c>
       <c r="E13" s="41" t="n">
-        <v>0.708</v>
+        <v>0.716</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>23</v>
+        <v>25.5</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
@@ -35667,25 +35690,25 @@
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>104</v>
+        <v>105.4</v>
       </c>
       <c r="D14" s="41" t="n">
-        <v>0.262</v>
+        <v>0.268</v>
       </c>
       <c r="E14" s="41" t="n">
-        <v>0.7759999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>96</v>
+        <v>110.5</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>22</v>
+        <v>25.5</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
@@ -35700,25 +35723,25 @@
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>103.8</v>
+        <v>105.4</v>
       </c>
       <c r="D15" s="41" t="n">
-        <v>0.323</v>
+        <v>0.29</v>
       </c>
       <c r="E15" s="41" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -35766,25 +35789,25 @@
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>109.6</v>
+        <v>108.7</v>
       </c>
       <c r="D17" s="41" t="n">
-        <v>0.103</v>
+        <v>0.224</v>
       </c>
       <c r="E17" s="41" t="n">
-        <v>0.638</v>
+        <v>0.6779999999999999</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>131</v>
+        <v>129.5</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>106</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="18">
@@ -35799,25 +35822,25 @@
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>105.7</v>
+        <v>109.3</v>
       </c>
       <c r="D18" s="41" t="n">
-        <v>0.289</v>
+        <v>0.276</v>
       </c>
       <c r="E18" s="41" t="n">
-        <v>0.7</v>
+        <v>0.7090000000000001</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>116</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="19">
@@ -35832,25 +35855,25 @@
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>109.6</v>
+        <v>105.6</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>0.362</v>
+        <v>0.375</v>
       </c>
       <c r="E19" s="41" t="n">
-        <v>0.897</v>
+        <v>0.86</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>106</v>
+        <v>99.5</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H19" s="40" t="n">
         <v>8</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -35865,25 +35888,25 @@
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>107.7</v>
+        <v>106.2</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>0.292</v>
+        <v>0.271</v>
       </c>
       <c r="E20" s="41" t="n">
-        <v>0.795</v>
+        <v>0.733</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>123</v>
+        <v>121.5</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>120</v>
+        <v>119.5</v>
       </c>
     </row>
     <row r="21">
@@ -35898,25 +35921,25 @@
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>107.8</v>
+        <v>101.8</v>
       </c>
       <c r="D21" s="41" t="n">
-        <v>0.264</v>
+        <v>0.283</v>
       </c>
       <c r="E21" s="41" t="n">
-        <v>0.867</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>100</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="22">
@@ -35964,25 +35987,25 @@
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>113.8</v>
+        <v>107.7</v>
       </c>
       <c r="D23" s="41" t="n">
-        <v>0.225</v>
+        <v>0.195</v>
       </c>
       <c r="E23" s="41" t="n">
-        <v>0.732</v>
+        <v>0.6629999999999999</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>132</v>
+        <v>123.5</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>28</v>
+        <v>30.5</v>
       </c>
       <c r="H23" s="40" t="n">
         <v>14</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24">
@@ -36162,25 +36185,25 @@
         </is>
       </c>
       <c r="C29" s="40" t="n">
-        <v>114.1</v>
+        <v>112.4</v>
       </c>
       <c r="D29" s="41" t="n">
-        <v>0.308</v>
+        <v>0.333</v>
       </c>
       <c r="E29" s="41" t="n">
-        <v>0.625</v>
+        <v>0.7190000000000001</v>
       </c>
       <c r="F29" s="40" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G29" s="40" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="H29" s="40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I29" s="40" t="n">
-        <v>135</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="30">
@@ -36195,25 +36218,25 @@
         </is>
       </c>
       <c r="C30" s="40" t="n">
-        <v>105</v>
+        <v>104.9</v>
       </c>
       <c r="D30" s="41" t="n">
-        <v>0.111</v>
+        <v>0.218</v>
       </c>
       <c r="E30" s="41" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.718</v>
       </c>
       <c r="F30" s="40" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G30" s="40" t="n">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="H30" s="40" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="I30" s="40" t="n">
-        <v>103</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="31">
@@ -36228,31 +36251,31 @@
         </is>
       </c>
       <c r="C31" s="40" t="n">
-        <v>105.7</v>
+        <v>108.3</v>
       </c>
       <c r="D31" s="41" t="n">
-        <v>0.3</v>
+        <v>0.225</v>
       </c>
       <c r="E31" s="41" t="n">
-        <v>0.711</v>
+        <v>0.6729999999999999</v>
       </c>
       <c r="F31" s="40" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G31" s="40" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="H31" s="40" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I31" s="40" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="31" t="inlineStr">
         <is>
-          <t>Fuente sugerida: teamrankings.com (Possessions per Game, Offensive/Defensive Rebounding %, Opponent Points/Assists/3PM per Game). Valores: temporada 2026-27, descargados 23-oct-2026 (muestra muy pequeña al inicio de temporada).</t>
+          <t>Fuente sugerida: teamrankings.com (Possessions per Game, Offensive/Defensive Rebounding %, Opponent Points/Assists/3PM per Game). Valores: temporada 2026-27, descargados 24-oct-2026 (muestra muy pequeña al inicio de temporada).</t>
         </is>
       </c>
     </row>
@@ -36451,6 +36474,23 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Usar ajuste por posición</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Sí = usa la defensa del rival contra la posición del jugador (hoja Defensa x Posicion). No = usa la defensa general del equipo.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
@@ -36464,7 +36504,7 @@
           <t>Pace promedio</t>
         </is>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="48">
         <f>AVERAGE('Stats Equipos'!C2:C31)</f>
         <v/>
       </c>
@@ -36475,7 +36515,7 @@
           <t>ORB% promedio</t>
         </is>
       </c>
-      <c r="B18" s="48">
+      <c r="B18" s="49">
         <f>AVERAGE('Stats Equipos'!D2:D31)</f>
         <v/>
       </c>
@@ -36486,7 +36526,7 @@
           <t>DRB% promedio</t>
         </is>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="49">
         <f>AVERAGE('Stats Equipos'!E2:E31)</f>
         <v/>
       </c>
@@ -36497,7 +36537,7 @@
           <t>Pts permitidos por posesión</t>
         </is>
       </c>
-      <c r="B20" s="49">
+      <c r="B20" s="50">
         <f>SUMPRODUCT('Stats Equipos'!F2:F31/'Stats Equipos'!C2:C31)/30</f>
         <v/>
       </c>
@@ -36508,7 +36548,7 @@
           <t>Ast permitidas por posesión</t>
         </is>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="50">
         <f>SUMPRODUCT('Stats Equipos'!G2:G31/'Stats Equipos'!C2:C31)/30</f>
         <v/>
       </c>
@@ -36519,7 +36559,7 @@
           <t>3PM permitidos por posesión</t>
         </is>
       </c>
-      <c r="B22" s="49">
+      <c r="B22" s="50">
         <f>SUMPRODUCT('Stats Equipos'!H2:H31/'Stats Equipos'!C2:C31)/30</f>
         <v/>
       </c>
@@ -36530,12 +36570,6220 @@
           <t>Pts anotados por posesión</t>
         </is>
       </c>
-      <c r="B23" s="49">
+      <c r="B23" s="50">
         <f>SUMPRODUCT('Stats Equipos'!I2:I31/'Stats Equipos'!C2:C31)/30</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Sí,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BK33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>Abrev</t>
+        </is>
+      </c>
+      <c r="B1" s="51" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="C1" s="51" t="inlineStr">
+        <is>
+          <t>PG PTS</t>
+        </is>
+      </c>
+      <c r="D1" s="51" t="inlineStr">
+        <is>
+          <t>PG REB</t>
+        </is>
+      </c>
+      <c r="E1" s="51" t="inlineStr">
+        <is>
+          <t>PG AST</t>
+        </is>
+      </c>
+      <c r="F1" s="51" t="inlineStr">
+        <is>
+          <t>PG 3PM</t>
+        </is>
+      </c>
+      <c r="G1" s="51" t="inlineStr">
+        <is>
+          <t>PG STL</t>
+        </is>
+      </c>
+      <c r="H1" s="51" t="inlineStr">
+        <is>
+          <t>PG BLK</t>
+        </is>
+      </c>
+      <c r="I1" s="51" t="inlineStr">
+        <is>
+          <t>SG PTS</t>
+        </is>
+      </c>
+      <c r="J1" s="51" t="inlineStr">
+        <is>
+          <t>SG REB</t>
+        </is>
+      </c>
+      <c r="K1" s="51" t="inlineStr">
+        <is>
+          <t>SG AST</t>
+        </is>
+      </c>
+      <c r="L1" s="51" t="inlineStr">
+        <is>
+          <t>SG 3PM</t>
+        </is>
+      </c>
+      <c r="M1" s="51" t="inlineStr">
+        <is>
+          <t>SG STL</t>
+        </is>
+      </c>
+      <c r="N1" s="51" t="inlineStr">
+        <is>
+          <t>SG BLK</t>
+        </is>
+      </c>
+      <c r="O1" s="51" t="inlineStr">
+        <is>
+          <t>SF PTS</t>
+        </is>
+      </c>
+      <c r="P1" s="51" t="inlineStr">
+        <is>
+          <t>SF REB</t>
+        </is>
+      </c>
+      <c r="Q1" s="51" t="inlineStr">
+        <is>
+          <t>SF AST</t>
+        </is>
+      </c>
+      <c r="R1" s="51" t="inlineStr">
+        <is>
+          <t>SF 3PM</t>
+        </is>
+      </c>
+      <c r="S1" s="51" t="inlineStr">
+        <is>
+          <t>SF STL</t>
+        </is>
+      </c>
+      <c r="T1" s="51" t="inlineStr">
+        <is>
+          <t>SF BLK</t>
+        </is>
+      </c>
+      <c r="U1" s="51" t="inlineStr">
+        <is>
+          <t>PF PTS</t>
+        </is>
+      </c>
+      <c r="V1" s="51" t="inlineStr">
+        <is>
+          <t>PF REB</t>
+        </is>
+      </c>
+      <c r="W1" s="51" t="inlineStr">
+        <is>
+          <t>PF AST</t>
+        </is>
+      </c>
+      <c r="X1" s="51" t="inlineStr">
+        <is>
+          <t>PF 3PM</t>
+        </is>
+      </c>
+      <c r="Y1" s="51" t="inlineStr">
+        <is>
+          <t>PF STL</t>
+        </is>
+      </c>
+      <c r="Z1" s="51" t="inlineStr">
+        <is>
+          <t>PF BLK</t>
+        </is>
+      </c>
+      <c r="AA1" s="51" t="inlineStr">
+        <is>
+          <t>C PTS</t>
+        </is>
+      </c>
+      <c r="AB1" s="51" t="inlineStr">
+        <is>
+          <t>C REB</t>
+        </is>
+      </c>
+      <c r="AC1" s="51" t="inlineStr">
+        <is>
+          <t>C AST</t>
+        </is>
+      </c>
+      <c r="AD1" s="51" t="inlineStr">
+        <is>
+          <t>C 3PM</t>
+        </is>
+      </c>
+      <c r="AE1" s="51" t="inlineStr">
+        <is>
+          <t>C STL</t>
+        </is>
+      </c>
+      <c r="AF1" s="51" t="inlineStr">
+        <is>
+          <t>C BLK</t>
+        </is>
+      </c>
+      <c r="AG1" s="51" t="inlineStr">
+        <is>
+          <t>Partidos</t>
+        </is>
+      </c>
+      <c r="AH1" s="51" t="inlineStr">
+        <is>
+          <t>PG PTS /partido</t>
+        </is>
+      </c>
+      <c r="AI1" s="51" t="inlineStr">
+        <is>
+          <t>PG REB /partido</t>
+        </is>
+      </c>
+      <c r="AJ1" s="51" t="inlineStr">
+        <is>
+          <t>PG AST /partido</t>
+        </is>
+      </c>
+      <c r="AK1" s="51" t="inlineStr">
+        <is>
+          <t>PG 3PM /partido</t>
+        </is>
+      </c>
+      <c r="AL1" s="51" t="inlineStr">
+        <is>
+          <t>PG STL /partido</t>
+        </is>
+      </c>
+      <c r="AM1" s="51" t="inlineStr">
+        <is>
+          <t>PG BLK /partido</t>
+        </is>
+      </c>
+      <c r="AN1" s="51" t="inlineStr">
+        <is>
+          <t>SG PTS /partido</t>
+        </is>
+      </c>
+      <c r="AO1" s="51" t="inlineStr">
+        <is>
+          <t>SG REB /partido</t>
+        </is>
+      </c>
+      <c r="AP1" s="51" t="inlineStr">
+        <is>
+          <t>SG AST /partido</t>
+        </is>
+      </c>
+      <c r="AQ1" s="51" t="inlineStr">
+        <is>
+          <t>SG 3PM /partido</t>
+        </is>
+      </c>
+      <c r="AR1" s="51" t="inlineStr">
+        <is>
+          <t>SG STL /partido</t>
+        </is>
+      </c>
+      <c r="AS1" s="51" t="inlineStr">
+        <is>
+          <t>SG BLK /partido</t>
+        </is>
+      </c>
+      <c r="AT1" s="51" t="inlineStr">
+        <is>
+          <t>SF PTS /partido</t>
+        </is>
+      </c>
+      <c r="AU1" s="51" t="inlineStr">
+        <is>
+          <t>SF REB /partido</t>
+        </is>
+      </c>
+      <c r="AV1" s="51" t="inlineStr">
+        <is>
+          <t>SF AST /partido</t>
+        </is>
+      </c>
+      <c r="AW1" s="51" t="inlineStr">
+        <is>
+          <t>SF 3PM /partido</t>
+        </is>
+      </c>
+      <c r="AX1" s="51" t="inlineStr">
+        <is>
+          <t>SF STL /partido</t>
+        </is>
+      </c>
+      <c r="AY1" s="51" t="inlineStr">
+        <is>
+          <t>SF BLK /partido</t>
+        </is>
+      </c>
+      <c r="AZ1" s="51" t="inlineStr">
+        <is>
+          <t>PF PTS /partido</t>
+        </is>
+      </c>
+      <c r="BA1" s="51" t="inlineStr">
+        <is>
+          <t>PF REB /partido</t>
+        </is>
+      </c>
+      <c r="BB1" s="51" t="inlineStr">
+        <is>
+          <t>PF AST /partido</t>
+        </is>
+      </c>
+      <c r="BC1" s="51" t="inlineStr">
+        <is>
+          <t>PF 3PM /partido</t>
+        </is>
+      </c>
+      <c r="BD1" s="51" t="inlineStr">
+        <is>
+          <t>PF STL /partido</t>
+        </is>
+      </c>
+      <c r="BE1" s="51" t="inlineStr">
+        <is>
+          <t>PF BLK /partido</t>
+        </is>
+      </c>
+      <c r="BF1" s="51" t="inlineStr">
+        <is>
+          <t>C PTS /partido</t>
+        </is>
+      </c>
+      <c r="BG1" s="51" t="inlineStr">
+        <is>
+          <t>C REB /partido</t>
+        </is>
+      </c>
+      <c r="BH1" s="51" t="inlineStr">
+        <is>
+          <t>C AST /partido</t>
+        </is>
+      </c>
+      <c r="BI1" s="51" t="inlineStr">
+        <is>
+          <t>C 3PM /partido</t>
+        </is>
+      </c>
+      <c r="BJ1" s="51" t="inlineStr">
+        <is>
+          <t>C STL /partido</t>
+        </is>
+      </c>
+      <c r="BK1" s="51" t="inlineStr">
+        <is>
+          <t>C BLK /partido</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="D2" s="52" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="E2" s="52" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="F2" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G2" s="52" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="H2" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I2" s="52" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="J2" s="52" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="K2" s="52" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L2" s="52" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="M2" s="52" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="N2" s="52" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="O2" s="52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P2" s="52" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="Q2" s="52" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="R2" s="52" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="S2" s="52" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="T2" s="52" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="U2" s="52" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="V2" s="52" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="W2" s="52" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="X2" s="52" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="Y2" s="52" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="Z2" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA2" s="52" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AB2" s="52" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="AC2" s="52" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="AD2" s="52" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="AE2" s="52" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="AF2" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG2" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI2" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ2" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK2" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM2" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO2" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP2" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR2" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT2" s="40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU2" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV2" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW2" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX2" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY2" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="40" t="n">
+        <v>35</v>
+      </c>
+      <c r="BA2" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB2" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC2" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD2" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG2" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH2" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI2" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ2" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK2" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="43" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C3" s="52" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="D3" s="52" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="E3" s="52" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="F3" s="52" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G3" s="52" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="H3" s="52" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="I3" s="52" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="J3" s="52" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="K3" s="52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L3" s="52" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="M3" s="52" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="N3" s="52" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="O3" s="52" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="P3" s="52" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="Q3" s="52" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="R3" s="52" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="S3" s="52" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="T3" s="52" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="U3" s="52" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="V3" s="52" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="W3" s="52" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="X3" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y3" s="52" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="Z3" s="52" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="AA3" s="52" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="AB3" s="52" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AC3" s="52" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="AD3" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE3" s="52" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="AF3" s="52" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="AG3" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ3" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK3" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO3" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AU3" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV3" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW3" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX3" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA3" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG3" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH3" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI3" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK3" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>BRK</t>
+        </is>
+      </c>
+      <c r="B4" s="43" t="inlineStr">
+        <is>
+          <t>Brooklyn Nets</t>
+        </is>
+      </c>
+      <c r="C4" s="52" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="D4" s="52" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E4" s="52" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="F4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G4" s="52" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="H4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I4" s="52" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="J4" s="52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K4" s="52" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="L4" s="52" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="M4" s="52" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="N4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O4" s="52" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="P4" s="52" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="Q4" s="52" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="R4" s="52" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="S4" s="52" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="T4" s="52" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="U4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="W4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="X4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z4" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA4" s="52" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="AB4" s="52" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="AC4" s="52" t="n">
+        <v>1.434</v>
+      </c>
+      <c r="AD4" s="52" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="AE4" s="52" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="AF4" s="52" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AG4" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI4" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ4" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO4" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP4" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ4" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU4" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="40" t="n">
+        <v>41</v>
+      </c>
+      <c r="BG4" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH4" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI4" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ4" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK4" s="40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C5" s="52" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="D5" s="52" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E5" s="52" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="F5" s="52" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="G5" s="52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H5" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I5" s="52" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="J5" s="52" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="K5" s="52" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="L5" s="52" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="M5" s="52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N5" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O5" s="52" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="P5" s="52" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="Q5" s="52" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="R5" s="52" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="S5" s="52" t="n">
+        <v>1.368</v>
+      </c>
+      <c r="T5" s="52" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="U5" s="52" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="V5" s="52" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="W5" s="52" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="X5" s="52" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="Y5" s="52" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="Z5" s="52" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="AA5" s="52" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="AB5" s="52" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="AC5" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AD5" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE5" s="52" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="AF5" s="52" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="AG5" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ5" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL5" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO5" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="40" t="n">
+        <v>51</v>
+      </c>
+      <c r="AU5" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV5" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX5" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="40" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA5" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB5" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF5" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG5" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>CHO</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C6" s="52" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="D6" s="52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E6" s="52" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="F6" s="52" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="G6" s="52" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="H6" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I6" s="52" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J6" s="52" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="K6" s="52" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="L6" s="52" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="M6" s="52" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="N6" s="52" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="O6" s="52" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="P6" s="52" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="Q6" s="52" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="R6" s="52" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="S6" s="52" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="T6" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U6" s="52" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="V6" s="52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W6" s="52" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="X6" s="52" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="Y6" s="52" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="Z6" s="52" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AA6" s="52" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="AB6" s="52" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="AC6" s="52" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="AD6" s="52" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="AE6" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF6" s="52" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="AG6" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI6" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ6" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU6" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="40" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA6" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB6" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC6" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF6" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG6" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH6" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" s="40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C7" s="52" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="D7" s="52" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E7" s="52" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="F7" s="52" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="G7" s="52" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="H7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I7" s="52" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="J7" s="52" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="K7" s="52" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="L7" s="52" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="M7" s="52" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="N7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O7" s="52" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="P7" s="52" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="Q7" s="52" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R7" s="52" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="S7" s="52" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="T7" s="52" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="U7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="W7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="X7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA7" s="52" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AB7" s="52" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="AC7" s="52" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AD7" s="52" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AE7" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF7" s="52" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="AG7" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI7" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO7" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP7" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU7" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV7" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX7" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG7" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C8" s="52" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="D8" s="52" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="E8" s="52" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="F8" s="52" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="G8" s="52" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="H8" s="52" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="I8" s="52" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="J8" s="52" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="K8" s="52" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="L8" s="52" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="M8" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N8" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O8" s="52" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="P8" s="52" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="Q8" s="52" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="R8" s="52" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="S8" s="52" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="T8" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U8" s="52" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="V8" s="52" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="W8" s="52" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="X8" s="52" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="Y8" s="52" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="Z8" s="52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA8" s="52" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="AB8" s="52" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="AC8" s="52" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AD8" s="52" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="AE8" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF8" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG8" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI8" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ8" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK8" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU8" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV8" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="40" t="n">
+        <v>62</v>
+      </c>
+      <c r="BA8" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB8" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC8" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD8" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF8" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG8" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH8" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="D9" s="52" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="E9" s="52" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="F9" s="52" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="G9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H9" s="52" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="I9" s="52" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="M9" s="52" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="N9" s="52" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="O9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="P9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U9" s="52" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="V9" s="52" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="W9" s="52" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="X9" s="52" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="Y9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA9" s="52" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="AB9" s="52" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="AC9" s="52" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AD9" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE9" s="52" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="AF9" s="52" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="AG9" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK9" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO9" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP9" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ9" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA9" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB9" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG9" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH9" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK9" s="40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="D10" s="52" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E10" s="52" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="F10" s="52" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I10" s="52" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="M10" s="52" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="N10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="P10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U10" s="52" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="V10" s="52" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="W10" s="52" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="X10" s="52" t="n">
+        <v>1.661</v>
+      </c>
+      <c r="Y10" s="52" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="Z10" s="52" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="AA10" s="52" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="AB10" s="52" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="AC10" s="52" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="AD10" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE10" s="52" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="AF10" s="52" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="AG10" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO10" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP10" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ10" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR10" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="40" t="n">
+        <v>62</v>
+      </c>
+      <c r="BA10" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB10" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC10" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD10" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF10" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG10" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH10" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK10" s="40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="D11" s="52" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="E11" s="52" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="F11" s="52" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="G11" s="52" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="H11" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I11" s="52" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K11" s="52" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="L11" s="52" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="M11" s="52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N11" s="52" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="O11" s="52" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="P11" s="52" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="Q11" s="52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R11" s="52" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="S11" s="52" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="T11" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U11" s="52" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="V11" s="52" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="W11" s="52" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="X11" s="52" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="Y11" s="52" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="Z11" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA11" s="52" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="AB11" s="52" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="AC11" s="52" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="AD11" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE11" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF11" s="52" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="AG11" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI11" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ11" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK11" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL11" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="40" t="n">
+        <v>43</v>
+      </c>
+      <c r="AO11" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP11" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ11" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR11" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS11" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT11" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB11" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC11" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD11" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG11" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH11" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="D12" s="52" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="E12" s="52" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="F12" s="52" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I12" s="52" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="J12" s="52" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="K12" s="52" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="L12" s="52" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="M12" s="52" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="N12" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O12" s="52" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="P12" s="52" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="Q12" s="52" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="R12" s="52" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="S12" s="52" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="T12" s="52" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="U12" s="52" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="V12" s="52" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="W12" s="52" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="X12" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z12" s="52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA12" s="52" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="AB12" s="52" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="AC12" s="52" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="AD12" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE12" s="52" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="AF12" s="52" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="AG12" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ12" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO12" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP12" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ12" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="40" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU12" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV12" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX12" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA12" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC12" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF12" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK12" s="40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D13" s="52" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="E13" s="52" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="F13" s="52" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="G13" s="52" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="H13" s="52" t="n">
+        <v>1.711</v>
+      </c>
+      <c r="I13" s="52" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="J13" s="52" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="K13" s="52" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="L13" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M13" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N13" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O13" s="52" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="P13" s="52" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="Q13" s="52" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="R13" s="52" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="S13" s="52" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="T13" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U13" s="52" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="V13" s="52" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="W13" s="52" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="X13" s="52" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="Y13" s="52" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="Z13" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA13" s="52" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="AB13" s="52" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="AC13" s="52" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="AD13" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE13" s="52" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="AF13" s="52" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AG13" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="40" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI13" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ13" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU13" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC13" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG13" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH13" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK13" s="40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D14" s="52" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="F14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I14" s="52" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="J14" s="52" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="K14" s="52" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="L14" s="52" t="n">
+        <v>1.072</v>
+      </c>
+      <c r="M14" s="52" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="N14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O14" s="52" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="P14" s="52" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Q14" s="52" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="R14" s="52" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="S14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U14" s="52" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="V14" s="52" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="W14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="X14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y14" s="52" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="Z14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA14" s="52" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="AB14" s="52" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AC14" s="52" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="AD14" s="52" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="AE14" s="52" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="AF14" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG14" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI14" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ14" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="40" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO14" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ14" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR14" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU14" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA14" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="40" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG14" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH14" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ14" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK14" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="D15" s="52" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="E15" s="52" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="F15" s="52" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="G15" s="52" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="H15" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I15" s="52" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="J15" s="52" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K15" s="52" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L15" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M15" s="52" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="N15" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O15" s="52" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="P15" s="52" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="Q15" s="52" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="R15" s="52" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="S15" s="52" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="T15" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U15" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="52" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="W15" s="52" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="X15" s="52" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="Y15" s="52" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="Z15" s="52" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AA15" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AB15" s="52" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="AC15" s="52" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="AD15" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE15" s="52" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="AF15" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG15" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="40" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI15" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ15" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK15" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO15" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV15" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA15" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB15" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH15" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK15" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="D16" s="52" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="E16" s="52" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="F16" s="52" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="G16" s="52" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="H16" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I16" s="52" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="J16" s="52" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="K16" s="52" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="L16" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M16" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N16" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O16" s="52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P16" s="52" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="Q16" s="52" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="R16" s="52" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="S16" s="52" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="T16" s="52" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="U16" s="52" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="V16" s="52" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="W16" s="52" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="X16" s="52" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="Y16" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z16" s="52" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="AA16" s="52" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="AB16" s="52" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="AC16" s="52" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="AD16" s="52" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="AE16" s="52" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="AF16" s="52" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="AG16" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI16" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ16" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK16" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL16" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO16" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP16" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU16" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV16" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW16" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX16" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY16" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ16" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA16" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB16" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF16" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG16" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH16" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI16" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ16" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK16" s="40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="D17" s="52" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E17" s="52" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="F17" s="52" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="G17" s="52" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="H17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I17" s="52" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="J17" s="52" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="K17" s="52" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="L17" s="52" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="M17" s="52" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="N17" s="52" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="O17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="P17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U17" s="52" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="V17" s="52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W17" s="52" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="X17" s="52" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="Y17" s="52" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="Z17" s="52" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="AA17" s="52" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AB17" s="52" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="AC17" s="52" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="AD17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF17" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG17" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI17" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK17" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL17" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="40" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO17" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP17" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ17" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR17" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS17" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA17" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB17" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC17" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD17" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE17" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF17" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG17" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH17" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="D18" s="52" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F18" s="52" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="G18" s="52" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="H18" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I18" s="52" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="J18" s="52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K18" s="52" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="L18" s="52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M18" s="52" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="N18" s="52" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="O18" s="52" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="P18" s="52" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="Q18" s="52" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R18" s="52" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="S18" s="52" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="T18" s="52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U18" s="52" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="V18" s="52" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="W18" s="52" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="X18" s="52" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="Y18" s="52" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="Z18" s="52" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="AA18" s="52" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="AB18" s="52" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="AC18" s="52" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="AD18" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE18" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF18" s="52" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="AG18" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL18" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO18" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP18" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT18" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU18" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX18" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ18" s="40" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA18" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB18" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF18" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG18" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH18" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" s="40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="D19" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="E19" s="52" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="F19" s="52" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G19" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H19" s="52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I19" s="52" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="J19" s="52" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="K19" s="52" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="L19" s="52" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="M19" s="52" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="N19" s="52" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="O19" s="52" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="P19" s="52" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="Q19" s="52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R19" s="52" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="S19" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T19" s="52" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="U19" s="52" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V19" s="52" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="W19" s="52" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="X19" s="52" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Y19" s="52" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="Z19" s="52" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="AA19" s="52" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="AB19" s="52" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="AC19" s="52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD19" s="52" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="AE19" s="52" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="AF19" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG19" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI19" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO19" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP19" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU19" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW19" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="40" t="n">
+        <v>46</v>
+      </c>
+      <c r="BA19" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB19" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE19" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF19" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG19" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH19" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ19" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK19" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>New Orleans Pelicans</t>
+        </is>
+      </c>
+      <c r="C20" s="52" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="D20" s="52" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="E20" s="52" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="F20" s="52" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="G20" s="52" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="H20" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I20" s="52" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="J20" s="52" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K20" s="52" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="L20" s="52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M20" s="52" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="N20" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O20" s="52" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="P20" s="52" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q20" s="52" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="R20" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S20" s="52" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="T20" s="52" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="U20" s="52" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V20" s="52" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="W20" s="52" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="X20" s="52" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="Y20" s="52" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="Z20" s="52" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="AA20" s="52" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="AB20" s="52" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="AC20" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AD20" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE20" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF20" s="52" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="AG20" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI20" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ20" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK20" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO20" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP20" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU20" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV20" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ20" s="40" t="n">
+        <v>53</v>
+      </c>
+      <c r="BA20" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB20" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC20" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD20" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF20" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG20" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" s="40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C21" s="52" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="D21" s="52" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E21" s="52" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="F21" s="52" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="G21" s="52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H21" s="52" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="I21" s="52" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="J21" s="52" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="K21" s="52" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="L21" s="52" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="M21" s="52" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="N21" s="52" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="O21" s="52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P21" s="52" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Q21" s="52" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="R21" s="52" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="S21" s="52" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="T21" s="52" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="U21" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V21" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="W21" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="X21" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y21" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z21" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA21" s="52" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="AB21" s="52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" s="52" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="AD21" s="52" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="AE21" s="52" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="AF21" s="52" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="AG21" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI21" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL21" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN21" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO21" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP21" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ21" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR21" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" s="40" t="n">
+        <v>33</v>
+      </c>
+      <c r="AU21" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV21" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW21" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX21" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY21" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG21" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH21" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI21" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ21" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK21" s="40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="C22" s="52" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="D22" s="52" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="E22" s="52" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="F22" s="52" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G22" s="52" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="H22" s="52" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="I22" s="52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J22" s="52" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="K22" s="52" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="L22" s="52" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="M22" s="52" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="N22" s="52" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="O22" s="52" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="P22" s="52" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="Q22" s="52" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="R22" s="52" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="S22" s="52" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="T22" s="52" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="U22" s="52" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="V22" s="52" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="W22" s="52" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="X22" s="52" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="Y22" s="52" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="Z22" s="52" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="AA22" s="52" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="AB22" s="52" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="AC22" s="52" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="AD22" s="52" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="AE22" s="52" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="AF22" s="52" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="AG22" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH22" s="40" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AI22" s="40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ22" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK22" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL22" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM22" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO22" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP22" s="40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS22" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" s="40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU22" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW22" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX22" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY22" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ22" s="40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA22" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB22" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC22" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF22" s="40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG22" s="40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH22" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI22" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BJ22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK22" s="40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C23" s="52" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="D23" s="52" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E23" s="52" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="F23" s="52" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="G23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H23" s="52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I23" s="52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J23" s="52" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="K23" s="52" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="L23" s="52" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="M23" s="52" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="N23" s="52" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="O23" s="52" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="P23" s="52" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="Q23" s="52" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="R23" s="52" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="S23" s="52" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="T23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="V23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="W23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="X23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA23" s="52" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AB23" s="52" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="AC23" s="52" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="AD23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE23" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF23" s="52" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="AG23" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI23" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ23" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK23" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="40" t="n">
+        <v>67</v>
+      </c>
+      <c r="AO23" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP23" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ23" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR23" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU23" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV23" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW23" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG23" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH23" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C24" s="52" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="D24" s="52" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="E24" s="52" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="F24" s="52" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="G24" s="52" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="H24" s="52" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="I24" s="52" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="J24" s="52" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="K24" s="52" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="L24" s="52" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="M24" s="52" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="N24" s="52" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="O24" s="52" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="P24" s="52" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="Q24" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R24" s="52" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="S24" s="52" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="T24" s="52" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="U24" s="52" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="V24" s="52" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="W24" s="52" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="X24" s="52" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="Y24" s="52" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="Z24" s="52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA24" s="52" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="AB24" s="52" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AC24" s="52" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="AD24" s="52" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="AE24" s="52" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AF24" s="52" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="AG24" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH24" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" s="40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ24" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK24" s="40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL24" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM24" s="40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN24" s="40" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AO24" s="40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP24" s="40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AQ24" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR24" s="40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS24" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT24" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU24" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV24" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AW24" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ24" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA24" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB24" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD24" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF24" s="40" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BG24" s="40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH24" s="40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI24" s="40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK24" s="40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>PHO</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="D25" s="52" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="E25" s="52" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="F25" s="52" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="G25" s="52" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="H25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="J25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="K25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="L25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O25" s="52" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="P25" s="52" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Q25" s="52" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="R25" s="52" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="S25" s="52" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="T25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U25" s="52" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="V25" s="52" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="W25" s="52" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="X25" s="52" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="Y25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA25" s="52" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AB25" s="52" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="AC25" s="52" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="AD25" s="52" t="n">
+        <v>1.434</v>
+      </c>
+      <c r="AE25" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF25" s="52" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="AG25" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="40" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI25" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ25" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK25" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL25" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU25" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV25" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW25" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX25" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA25" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB25" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC25" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG25" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH25" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI25" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C26" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D26" s="52" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="E26" s="52" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="F26" s="52" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G26" s="52" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="H26" s="52" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="I26" s="52" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="J26" s="52" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="K26" s="52" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="L26" s="52" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="M26" s="52" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="N26" s="52" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="O26" s="52" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="P26" s="52" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="Q26" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R26" s="52" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="S26" s="52" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="T26" s="52" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="U26" s="52" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="V26" s="52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W26" s="52" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="X26" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Y26" s="52" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="Z26" s="52" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="AA26" s="52" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="AB26" s="52" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="AC26" s="52" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="AD26" s="52" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="AE26" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF26" s="52" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="AG26" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI26" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ26" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK26" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL26" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="40" t="n">
+        <v>33</v>
+      </c>
+      <c r="AO26" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP26" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ26" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT26" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU26" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV26" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ26" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB26" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC26" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF26" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG26" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ26" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C27" s="52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D27" s="52" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="E27" s="52" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="F27" s="52" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="G27" s="52" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="H27" s="52" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="I27" s="52" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="J27" s="52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K27" s="52" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="L27" s="52" t="n">
+        <v>1.072</v>
+      </c>
+      <c r="M27" s="52" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="N27" s="52" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="O27" s="52" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="P27" s="52" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="Q27" s="52" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="R27" s="52" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="S27" s="52" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="T27" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U27" s="52" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="V27" s="52" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="W27" s="52" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="X27" s="52" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="Y27" s="52" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="Z27" s="52" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AA27" s="52" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="AB27" s="52" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="AC27" s="52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AD27" s="52" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="AE27" s="52" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="AF27" s="52" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="AG27" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="40" t="n">
+        <v>37</v>
+      </c>
+      <c r="AI27" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ27" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK27" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL27" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM27" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN27" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO27" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP27" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ27" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR27" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU27" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV27" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY27" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA27" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB27" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC27" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF27" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG27" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ27" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK27" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C28" s="52" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="D28" s="52" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E28" s="52" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="F28" s="52" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="G28" s="52" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="H28" s="52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I28" s="52" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J28" s="52" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="K28" s="52" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="L28" s="52" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="M28" s="52" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="N28" s="52" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="O28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="P28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U28" s="52" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="V28" s="52" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="W28" s="52" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="X28" s="52" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="Y28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA28" s="52" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="AB28" s="52" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="AC28" s="52" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD28" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE28" s="52" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="AF28" s="52" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AG28" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI28" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ28" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK28" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL28" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN28" s="40" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO28" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP28" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ28" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR28" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA28" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG28" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH28" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK28" s="40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="C29" s="52" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="D29" s="52" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="E29" s="52" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="F29" s="52" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="G29" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H29" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I29" s="52" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="J29" s="52" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="K29" s="52" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="L29" s="52" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="M29" s="52" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="N29" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O29" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="52" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="Q29" s="52" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="R29" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S29" s="52" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="T29" s="52" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="U29" s="52" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="V29" s="52" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="W29" s="52" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="X29" s="52" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="Y29" s="52" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="Z29" s="52" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="AA29" s="52" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="AB29" s="52" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="AC29" s="52" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AD29" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AE29" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF29" s="52" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="AG29" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI29" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ29" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO29" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP29" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ29" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR29" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU29" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ29" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA29" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB29" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD29" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE29" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF29" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG29" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C30" s="52" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="D30" s="52" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="E30" s="52" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="F30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="G30" s="52" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="H30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I30" s="52" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="J30" s="52" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="K30" s="52" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="L30" s="52" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="M30" s="52" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="N30" s="52" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="O30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="P30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U30" s="52" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="V30" s="52" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="W30" s="52" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="X30" s="52" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="Y30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Z30" s="52" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="AA30" s="52" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="AB30" s="52" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="AC30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AD30" s="52" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="AE30" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AF30" s="52" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AG30" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH30" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI30" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ30" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="40" t="n">
+        <v>67</v>
+      </c>
+      <c r="AO30" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP30" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ30" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR30" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS30" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" s="40" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA30" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB30" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC30" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF30" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG30" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" s="40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Washington Wizards</t>
+        </is>
+      </c>
+      <c r="C31" s="52" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="D31" s="52" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="E31" s="52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F31" s="52" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="G31" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H31" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="I31" s="52" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="J31" s="52" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="K31" s="52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L31" s="52" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="M31" s="52" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="N31" s="52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O31" s="52" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="P31" s="52" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="Q31" s="52" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R31" s="52" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="S31" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="T31" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="U31" s="52" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="V31" s="52" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="W31" s="52" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="X31" s="52" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="Y31" s="52" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="Z31" s="52" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AA31" s="52" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="AB31" s="52" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="AC31" s="52" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="AD31" s="52" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="AE31" s="52" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="AF31" s="52" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="AG31" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI31" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ31" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="40" t="n">
+        <v>57</v>
+      </c>
+      <c r="AO31" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP31" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ31" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU31" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA31" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB31" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD31" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG31" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH31" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI31" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK31" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>Factor = lo que el equipo permite a esa posición por posesión ÷ promedio de liga (1.20 = permite 20% más; verde = bueno para apostar Over). Con pocos partidos se acerca a 1.00 (se mezcla con 5 partidos de promedio de liga). Calculado con 16 box scores de basketball-reference.com, 24-oct-2026. La posición de cada jugador es la de basketball-reference (la primera si tiene dos).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:AF31">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0.8"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="1.2"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>